--- a/MVPlate/MV_InputTemplate.xlsx
+++ b/MVPlate/MV_InputTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebas\OneDrive\Documents\WebServer\ot2\MVPlate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jornb\Documents\GitHub\ot2vanhasselt\MVPlate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCA68C1-E850-4586-A7D4-64FAD41641C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0581B08-BA27-43C3-A8EF-B61C094D2522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33315" yWindow="4035" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="39">
   <si>
     <t>Drug Name</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>1000,5</t>
+  </si>
+  <si>
+    <t>&gt;For controls that you don’t want to randomize use "control" or "ctrl"</t>
   </si>
 </sst>
 </file>
@@ -271,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -290,17 +293,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -316,9 +317,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Thema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -356,7 +357,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -462,7 +463,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -604,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -667,7 +668,7 @@
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
-      <c r="O2" s="9">
+      <c r="O2" s="8">
         <v>1</v>
       </c>
     </row>
@@ -694,12 +695,12 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
-      <c r="O3" s="9">
+      <c r="O3" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O4" s="9">
+      <c r="O4" s="8">
         <v>3</v>
       </c>
     </row>
@@ -710,16 +711,16 @@
       <c r="C5" s="5">
         <v>200</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="N5" s="9" t="s">
+      <c r="H5" s="8"/>
+      <c r="N5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="5">
@@ -728,22 +729,22 @@
       <c r="D6" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>2</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="H7" s="9"/>
-      <c r="O7" s="9">
+      <c r="H7" s="8"/>
+      <c r="O7" s="8">
         <v>6</v>
       </c>
     </row>
@@ -751,8 +752,8 @@
       <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="O8" s="9"/>
+      <c r="H8" s="8"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
@@ -808,7 +809,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="O10" s="11" t="s">
+      <c r="O10" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -846,7 +847,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
-      <c r="O11" s="11" t="s">
+      <c r="O11" s="10" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1125,7 +1126,7 @@
       <c r="M21" s="2">
         <v>0</v>
       </c>
-      <c r="O21" s="11" t="s">
+      <c r="O21" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1172,7 +1173,7 @@
       <c r="M22" s="2">
         <v>0</v>
       </c>
-      <c r="O22" s="11" t="s">
+      <c r="O22" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1520,7 +1521,7 @@
       <c r="M33" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O33" s="11" t="s">
+      <c r="O33" s="10" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1870,7 +1871,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
-      <c r="O45" s="11" t="s">
+      <c r="O45" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1908,7 +1909,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
-      <c r="O46" s="12" t="s">
+      <c r="O46" s="11" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1946,7 +1947,7 @@
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
-      <c r="O47" s="11" t="s">
+      <c r="O47" s="10" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1984,6 +1985,9 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
+      <c r="O48" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
@@ -2583,4 +2587,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d465f887-04a9-4c17-8b62-103eddccf68b}" enabled="1" method="Standard" siteId="{ca2a7f76-dbd7-4ec0-9108-6b3d524fb7c8}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>